--- a/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-101715</t>
+          <t>I-101897</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.0470386</t>
+          <t>-12.0420571</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.9739023</t>
+          <t>-76.9786085</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Calle Antonio Portugal / Calle Los Nogales</t>
+          <t>Avenida José Carlos Mariátegui / Jirón Luis de la Puente Uceda</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-101897</t>
+          <t>I-138899</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.0420571</t>
+          <t>-12.0403762</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.9786085</t>
+          <t>-76.9644544</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida José Carlos Mariátegui / Jr. Luis de la Puente Uceda</t>
+          <t>Avenida Imperial / Chasquis</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-107286</t>
+          <t>I-374820</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.0408346</t>
+          <t>-12.0532552</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.9642593</t>
+          <t>-76.9630146</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Gran Chimu / Avenida Imperial</t>
+          <t>Zorzales / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-107287</t>
+          <t>I-14938</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,22 +664,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.0407878</t>
+          <t>-12.0570892</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.9641457</t>
+          <t>-76.9724967</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Gran Chimu / Avenida Imperial</t>
+          <t>Avenida Los Cipreses / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-138899</t>
+          <t>I-161041</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.0403762</t>
+          <t>-12.0452327</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.9644544</t>
+          <t>-76.9616048</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Imperial / Chasquis</t>
+          <t>Avenida Los Rosales / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-138900</t>
+          <t>I-205175</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.0403301</t>
+          <t>-12.0425705</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.9643393</t>
+          <t>-76.9776864</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Imperial / Chasquis</t>
+          <t>Avenida José Carlos Mariátegui / Los Incas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-151258</t>
+          <t>I-205173</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,22 +820,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.0312542</t>
+          <t>-12.0431145</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-76.9504861</t>
+          <t>-76.9798594</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida C / Avenida de La Cultura</t>
+          <t>Calle Cesar Vallejo / Jirón Luis de la Puente Uceda</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-151741</t>
+          <t>I-205171</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,233 +872,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.0529416</t>
+          <t>-12.0424442</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-76.9634895</t>
+          <t>-76.9796551</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Faisanes / Golondrinas</t>
+          <t>1 de Mayo / Calle Ciro Alegria</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>l-151743</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-12.0532836</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-76.9633258</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Golondrinas / Zorzales</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>l-374820</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-12.0532552</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-76.9630146</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Zorzales</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>l-99080</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-12.0433684</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-76.9717821</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Jr. Jesús Páez / Satuchi</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>l-99412</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-12.0528138</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-76.963169</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>El Reyzuelo / Faisanes</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
         <is>
           <t>150137</t>
         </is>

--- a/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SANTA_ANITA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-101897</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-12.0420571</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>150137</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SANTA_ANITA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-138899</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-12.0403762</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>150137</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SANTA_ANITA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-374820</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-12.0532552</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>150137</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SANTA_ANITA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-14938</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-12.0570892</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>150137</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SANTA_ANITA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-161041</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-12.0452327</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>150137</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SANTA_ANITA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-205175</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-12.0425705</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>150137</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SANTA_ANITA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-205173</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-12.0431145</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>150137</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SANTA_ANITA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-205171</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SANTA ANITA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-12.0424442</t>
@@ -888,11 +848,6 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>150137</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -839,6 +839,147 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SANTA ANITA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>I-102335</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-12.0428884</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-76.9815808</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>JIRON JOSE OLAYA CON JR MANUEL GONZALES PRADA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SANTA ANITA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>I-99320</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-12.0508612</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-76.9648594</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CALLE LOS FLAMENCOS CON AV. CASCANUECES</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SANTA ANITA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>I-106428</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-12.0527</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-76.9789763</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>JR. PALMERAS CON CALLE DELICIAS</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -867,17 +867,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.0428884</t>
+          <t>-12.04627325</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-76.9815808</t>
+          <t>-76.97581532</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>JIRON JOSE OLAYA CON JR MANUEL GONZALES PRADA</t>
+          <t>Jr. Vargas Machuca con Jr. Los Alcanfores</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,17 +961,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-12.0527</t>
+          <t>-12.05123689</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-76.9789763</t>
+          <t>-76.97730733</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>JR. PALMERAS CON CALLE DELICIAS</t>
+          <t>Av. 1ro de Mayo con Jr. Palmeras</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-101897</t>
+          <t>I-99320</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.0420571</t>
+          <t>-12.0508612</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.9786085</t>
+          <t>-76.9648594</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida José Carlos Mariátegui / Jirón Luis de la Puente Uceda</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-138899</t>
+          <t>I-374820</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.0403762</t>
+          <t>-12.0532552</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.9644544</t>
+          <t>-76.9630146</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Imperial / Chasquis</t>
+          <t>Zorzales / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-374820</t>
+          <t>I-205175</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.0532552</t>
+          <t>-12.0425705</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.9630146</t>
+          <t>-76.9776864</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Zorzales / Calle s / n</t>
+          <t>Avenida José Carlos Mariátegui / Los Incas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-14938</t>
+          <t>I-205173</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.0570892</t>
+          <t>-12.0431145</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.9724967</t>
+          <t>-76.9798594</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Los Cipreses / Calle s / n</t>
+          <t>Calle Cesar Vallejo / Jirón Luis de la Puente Uceda</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-161041</t>
+          <t>I-205171</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.0452327</t>
+          <t>-12.0424442</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.9616048</t>
+          <t>-76.9796551</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Los Rosales / Calle s / n</t>
+          <t>1 de Mayo / Calle Ciro Alegria</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-205175</t>
+          <t>I-161041</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.0425705</t>
+          <t>-12.0452327</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.9776864</t>
+          <t>-76.9616048</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida José Carlos Mariátegui / Los Incas</t>
+          <t>Avenida Los Rosales / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-205173</t>
+          <t>I-14939</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.0431145</t>
+          <t>-12.0574582</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-76.9798594</t>
+          <t>-76.9716404</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Calle Cesar Vallejo / Jirón Luis de la Puente Uceda</t>
+          <t>Avenida Los Cipreses / Avenida Minería</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-205171</t>
+          <t>I-14938</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.0424442</t>
+          <t>-12.0570892</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-76.9796551</t>
+          <t>-76.9724967</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1 de Mayo / Calle Ciro Alegria</t>
+          <t>Avenida Los Cipreses / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,27 +862,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-102335</t>
+          <t>I-138899</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.04627325</t>
+          <t>-12.0403762</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-76.97581532</t>
+          <t>-76.9644544</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Jr. Vargas Machuca con Jr. Los Alcanfores</t>
+          <t>Avenida Imperial / Chasquis</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-99320</t>
+          <t>I-106428</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-12.0508612</t>
+          <t>-12.05123689</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-76.9648594</t>
+          <t>-76.97730733</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CALLE LOS FLAMENCOS CON AV. CASCANUECES</t>
+          <t>Av. 1ro de Mayo con Jr. Palmeras</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,27 +956,74 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-106428</t>
+          <t>I-102335</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-12.05123689</t>
+          <t>-12.04627325</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-76.97730733</t>
+          <t>-76.97581532</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Av. 1ro de Mayo con Jr. Palmeras</t>
+          <t>Jr. Vargas Machuca con Jr. Los Alcanfores</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>150137</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SANTA ANITA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>I-101897</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-12.0420571</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-76.9786085</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Avenida José Carlos Mariátegui / Jirón Luis de la Puente Uceda</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
